--- a/synthetic/output/assignments/assignments.xlsx
+++ b/synthetic/output/assignments/assignments.xlsx
@@ -454,7 +454,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FR0007</t>
+          <t>FR0002</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -479,7 +479,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FR0002</t>
+          <t>FR0007</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -504,7 +504,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FR0006</t>
+          <t>FR0004</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FR0006</t>
+          <t>FR0009</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -579,7 +579,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FR0001</t>
+          <t>FR0010</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>FR0002</t>
+          <t>FR0006</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FR0009</t>
+          <t>FR0001</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FR0006</t>
+          <t>FR0008</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">

--- a/synthetic/output/assignments/assignments.xlsx
+++ b/synthetic/output/assignments/assignments.xlsx
@@ -449,239 +449,259 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A000001</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>FR0014</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>D000001</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A000002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FR0028</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>D000002</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A000003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FR0022</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>D000003</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A000004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>FR0002</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>D000001</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>D000004</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A000005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FR0024</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>D000005</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A000006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>FR0026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>D000006</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A000007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>FR0008</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>D000007</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A000008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>FR0007</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>D000002</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>FR0004</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>D000003</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>FR0009</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>D000004</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>FR0008</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>D000005</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>FR0010</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>D000006</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>D000008</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A000009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FR0005</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>D000009</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Inactive</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A000010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>FR0006</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>D000007</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>FR0008</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>D000008</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>FR0001</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>D000009</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>1</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>FR0008</t>
-        </is>
-      </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>D000010</t>
@@ -694,7 +714,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
